--- a/artfynd/A 57597-2023 artfynd.xlsx
+++ b/artfynd/A 57597-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113713948</v>
+        <v>113713947</v>
       </c>
       <c r="B2" t="n">
-        <v>56831</v>
+        <v>90412</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100110</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647190</v>
+        <v>647159</v>
       </c>
       <c r="R2" t="n">
-        <v>7037704</v>
+        <v>7037736</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En hane</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711829</v>
+        <v>113711501</v>
       </c>
       <c r="B3" t="n">
-        <v>90412</v>
+        <v>90131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647159</v>
+        <v>647171</v>
       </c>
       <c r="R3" t="n">
-        <v>7037736</v>
+        <v>7037732</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711828</v>
+        <v>113711830</v>
       </c>
       <c r="B4" t="n">
-        <v>90131</v>
+        <v>56831</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647171</v>
+        <v>647190</v>
       </c>
       <c r="R4" t="n">
-        <v>7037732</v>
+        <v>7037704</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En hane</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57597-2023 artfynd.xlsx
+++ b/artfynd/A 57597-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113713947</v>
+        <v>113711502</v>
       </c>
       <c r="B2" t="n">
-        <v>90412</v>
+        <v>90416</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711501</v>
+        <v>113713946</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711830</v>
+        <v>113711503</v>
       </c>
       <c r="B4" t="n">
         <v>56831</v>

--- a/artfynd/A 57597-2023 artfynd.xlsx
+++ b/artfynd/A 57597-2023 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713946</v>
+        <v>113711828</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 57597-2023 artfynd.xlsx
+++ b/artfynd/A 57597-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711502</v>
+        <v>113711503</v>
       </c>
       <c r="B2" t="n">
-        <v>90416</v>
+        <v>56831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647159</v>
+        <v>647190</v>
       </c>
       <c r="R2" t="n">
-        <v>7037736</v>
+        <v>7037704</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En hane</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711828</v>
+        <v>113711501</v>
       </c>
       <c r="B3" t="n">
         <v>90135</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711503</v>
+        <v>113711829</v>
       </c>
       <c r="B4" t="n">
-        <v>56831</v>
+        <v>90416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100110</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647190</v>
+        <v>647159</v>
       </c>
       <c r="R4" t="n">
-        <v>7037704</v>
+        <v>7037736</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En hane</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57597-2023 artfynd.xlsx
+++ b/artfynd/A 57597-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711503</v>
+        <v>113713948</v>
       </c>
       <c r="B2" t="n">
         <v>56831</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711501</v>
+        <v>113713947</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647171</v>
+        <v>647159</v>
       </c>
       <c r="R3" t="n">
-        <v>7037732</v>
+        <v>7037736</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711829</v>
+        <v>113713946</v>
       </c>
       <c r="B4" t="n">
-        <v>90416</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647159</v>
+        <v>647171</v>
       </c>
       <c r="R4" t="n">
-        <v>7037736</v>
+        <v>7037732</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 57597-2023 artfynd.xlsx
+++ b/artfynd/A 57597-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113713948</v>
+        <v>113713946</v>
       </c>
       <c r="B2" t="n">
-        <v>56831</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100110</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647190</v>
+        <v>647171</v>
       </c>
       <c r="R2" t="n">
-        <v>7037704</v>
+        <v>7037732</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En hane</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713947</v>
+        <v>113711503</v>
       </c>
       <c r="B3" t="n">
-        <v>90416</v>
+        <v>56831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>100110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647159</v>
+        <v>647190</v>
       </c>
       <c r="R3" t="n">
-        <v>7037736</v>
+        <v>7037704</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,6 +859,11 @@
           <t>2023-10-25</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En hane</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,7 +881,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713946</v>
+        <v>113711502</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>90416</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647171</v>
+        <v>647159</v>
       </c>
       <c r="R4" t="n">
-        <v>7037732</v>
+        <v>7037736</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 57597-2023 artfynd.xlsx
+++ b/artfynd/A 57597-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
